--- a/Data/Export/Language/100_BuildingWorking_建筑工作.xlsx
+++ b/Data/Export/Language/100_BuildingWorking_建筑工作.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Language\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE3E2B6-45E9-4B34-B160-604574ED47D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F384362-F2C7-4826-AA85-7AC0A079F2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="2415" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingWorking" sheetId="36" r:id="rId1"/>
@@ -62,14 +62,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>工作/设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作/自动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -95,6 +87,14 @@
   </si>
   <si>
     <t>内政方式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作设置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动工作</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -224,7 +224,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -258,9 +258,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -580,7 +577,7 @@
   <cols>
     <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -620,7 +617,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -636,7 +633,7 @@
       <c r="B4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
     </row>
@@ -644,8 +641,8 @@
       <c r="B5" s="4">
         <v>10000001</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>7</v>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -657,8 +654,8 @@
       <c r="B6" s="4">
         <v>10000002</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>8</v>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -669,8 +666,8 @@
       <c r="B7" s="4">
         <v>10000003</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>10</v>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -681,8 +678,8 @@
       <c r="B8" s="4">
         <v>10000004</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>11</v>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -693,8 +690,8 @@
       <c r="B9" s="4">
         <v>10000005</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>12</v>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -705,8 +702,8 @@
       <c r="B10" s="4">
         <v>10000006</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>13</v>
+      <c r="C10" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -717,8 +714,8 @@
       <c r="B11" s="4">
         <v>10000008</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>14</v>
+      <c r="C11" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -729,8 +726,8 @@
       <c r="B12" s="4">
         <v>10000009</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>15</v>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -741,8 +738,8 @@
       <c r="B13" s="4">
         <v>10000010</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>16</v>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
